--- a/military_drill_pay.xlsx
+++ b/military_drill_pay.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1367003460.MIL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAACCACE-8C64-4C64-A25E-DDF0179C0675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9BDF83-FB64-4DC2-BB7F-A4186A740123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5235" yWindow="5055" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$EF$22:$EN$43</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -89,10 +92,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -118,9 +127,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EZ26"/>
+  <dimension ref="A1:FU25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
@@ -443,7 +453,7 @@
     <col min="46" max="46" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -909,8 +919,74 @@
       <c r="EY1">
         <v>40</v>
       </c>
+      <c r="EZ1">
+        <v>0</v>
+      </c>
+      <c r="FA1">
+        <v>2</v>
+      </c>
+      <c r="FB1">
+        <v>3</v>
+      </c>
+      <c r="FC1">
+        <v>4</v>
+      </c>
+      <c r="FD1">
+        <v>6</v>
+      </c>
+      <c r="FE1">
+        <v>8</v>
+      </c>
+      <c r="FF1">
+        <v>10</v>
+      </c>
+      <c r="FG1">
+        <v>12</v>
+      </c>
+      <c r="FH1">
+        <v>14</v>
+      </c>
+      <c r="FI1">
+        <v>16</v>
+      </c>
+      <c r="FJ1">
+        <v>18</v>
+      </c>
+      <c r="FK1">
+        <v>20</v>
+      </c>
+      <c r="FL1">
+        <v>22</v>
+      </c>
+      <c r="FM1">
+        <v>24</v>
+      </c>
+      <c r="FN1">
+        <v>26</v>
+      </c>
+      <c r="FO1">
+        <v>28</v>
+      </c>
+      <c r="FP1">
+        <v>30</v>
+      </c>
+      <c r="FQ1">
+        <v>32</v>
+      </c>
+      <c r="FR1">
+        <v>34</v>
+      </c>
+      <c r="FS1">
+        <v>36</v>
+      </c>
+      <c r="FT1">
+        <v>38</v>
+      </c>
+      <c r="FU1">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1376,8 +1452,74 @@
       <c r="EY2">
         <v>441.51</v>
       </c>
+      <c r="EZ2" s="2">
+        <v>288.02</v>
+      </c>
+      <c r="FA2" s="2">
+        <v>301.39</v>
+      </c>
+      <c r="FB2" s="2">
+        <v>307.58999999999997</v>
+      </c>
+      <c r="FC2" s="2">
+        <v>312.51</v>
+      </c>
+      <c r="FD2" s="2">
+        <v>321.42</v>
+      </c>
+      <c r="FE2" s="2">
+        <v>330.23</v>
+      </c>
+      <c r="FF2" s="2">
+        <v>340.41</v>
+      </c>
+      <c r="FG2" s="2">
+        <v>350.56</v>
+      </c>
+      <c r="FH2" s="2">
+        <v>360.74</v>
+      </c>
+      <c r="FI2" s="2">
+        <v>392.73</v>
+      </c>
+      <c r="FJ2" s="2">
+        <v>419.73</v>
+      </c>
+      <c r="FK2" s="2">
+        <v>419.73</v>
+      </c>
+      <c r="FL2" s="2">
+        <v>419.73</v>
+      </c>
+      <c r="FM2" s="2">
+        <v>419.73</v>
+      </c>
+      <c r="FN2" s="2">
+        <v>421.88</v>
+      </c>
+      <c r="FO2" s="2">
+        <v>421.88</v>
+      </c>
+      <c r="FP2" s="2">
+        <v>430.32</v>
+      </c>
+      <c r="FQ2" s="2">
+        <v>430.32</v>
+      </c>
+      <c r="FR2" s="2">
+        <v>430.32</v>
+      </c>
+      <c r="FS2" s="2">
+        <v>430.32</v>
+      </c>
+      <c r="FT2" s="2">
+        <v>430.32</v>
+      </c>
+      <c r="FU2" s="2">
+        <v>430.32</v>
+      </c>
     </row>
-    <row r="3" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1843,8 +1985,74 @@
       <c r="EY3">
         <v>396.71</v>
       </c>
+      <c r="EZ3" s="2">
+        <v>218.41</v>
+      </c>
+      <c r="FA3" s="2">
+        <v>239.95</v>
+      </c>
+      <c r="FB3" s="2">
+        <v>255.7</v>
+      </c>
+      <c r="FC3" s="2">
+        <v>255.7</v>
+      </c>
+      <c r="FD3" s="2">
+        <v>256.68</v>
+      </c>
+      <c r="FE3" s="2">
+        <v>267.68</v>
+      </c>
+      <c r="FF3" s="2">
+        <v>269.13</v>
+      </c>
+      <c r="FG3" s="2">
+        <v>269.13</v>
+      </c>
+      <c r="FH3" s="2">
+        <v>284.42</v>
+      </c>
+      <c r="FI3" s="2">
+        <v>311.45999999999998</v>
+      </c>
+      <c r="FJ3" s="2">
+        <v>327.33</v>
+      </c>
+      <c r="FK3" s="2">
+        <v>343.19</v>
+      </c>
+      <c r="FL3" s="2">
+        <v>352.22</v>
+      </c>
+      <c r="FM3" s="2">
+        <v>361.37</v>
+      </c>
+      <c r="FN3" s="2">
+        <v>379.08</v>
+      </c>
+      <c r="FO3" s="2">
+        <v>379.08</v>
+      </c>
+      <c r="FP3" s="2">
+        <v>386.66</v>
+      </c>
+      <c r="FQ3" s="2">
+        <v>386.66</v>
+      </c>
+      <c r="FR3" s="2">
+        <v>386.66</v>
+      </c>
+      <c r="FS3" s="2">
+        <v>386.66</v>
+      </c>
+      <c r="FT3" s="2">
+        <v>386.66</v>
+      </c>
+      <c r="FU3" s="2">
+        <v>386.66</v>
+      </c>
     </row>
-    <row r="4" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2310,8 +2518,74 @@
       <c r="EY4">
         <v>317.38</v>
       </c>
+      <c r="EZ4" s="2">
+        <v>182.08</v>
+      </c>
+      <c r="FA4" s="2">
+        <v>205.12</v>
+      </c>
+      <c r="FB4" s="2">
+        <v>219.3</v>
+      </c>
+      <c r="FC4" s="2">
+        <v>221.98</v>
+      </c>
+      <c r="FD4" s="2">
+        <v>230.85</v>
+      </c>
+      <c r="FE4" s="2">
+        <v>236.14</v>
+      </c>
+      <c r="FF4" s="2">
+        <v>247.8</v>
+      </c>
+      <c r="FG4" s="2">
+        <v>256.36</v>
+      </c>
+      <c r="FH4" s="2">
+        <v>267.41000000000003</v>
+      </c>
+      <c r="FI4" s="2">
+        <v>284.32</v>
+      </c>
+      <c r="FJ4" s="2">
+        <v>292.35000000000002</v>
+      </c>
+      <c r="FK4" s="2">
+        <v>300.31</v>
+      </c>
+      <c r="FL4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FM4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FN4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FO4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FP4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FQ4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FR4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FS4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FT4" s="2">
+        <v>309.33999999999997</v>
+      </c>
+      <c r="FU4" s="2">
+        <v>309.33999999999997</v>
+      </c>
     </row>
-    <row r="5" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2777,8 +3051,74 @@
       <c r="EY5">
         <v>269.13</v>
       </c>
+      <c r="EZ5" s="2">
+        <v>157.1</v>
+      </c>
+      <c r="FA5" s="2">
+        <v>181.85</v>
+      </c>
+      <c r="FB5" s="2">
+        <v>194</v>
+      </c>
+      <c r="FC5" s="2">
+        <v>196.69</v>
+      </c>
+      <c r="FD5" s="2">
+        <v>207.95</v>
+      </c>
+      <c r="FE5" s="2">
+        <v>220.04</v>
+      </c>
+      <c r="FF5" s="2">
+        <v>235.09</v>
+      </c>
+      <c r="FG5" s="2">
+        <v>246.79</v>
+      </c>
+      <c r="FH5" s="2">
+        <v>254.92</v>
+      </c>
+      <c r="FI5" s="2">
+        <v>259.60000000000002</v>
+      </c>
+      <c r="FJ5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FK5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FL5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FM5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FN5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FO5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FP5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FQ5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FR5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FS5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FT5" s="2">
+        <v>262.31</v>
+      </c>
+      <c r="FU5" s="2">
+        <v>262.31</v>
+      </c>
     </row>
-    <row r="6" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3244,8 +3584,74 @@
       <c r="EY6">
         <v>230.56</v>
       </c>
+      <c r="EZ6" s="2">
+        <v>138.13</v>
+      </c>
+      <c r="FA6" s="2">
+        <v>156.57</v>
+      </c>
+      <c r="FB6" s="2">
+        <v>168.99</v>
+      </c>
+      <c r="FC6" s="2">
+        <v>184.26</v>
+      </c>
+      <c r="FD6" s="2">
+        <v>193.1</v>
+      </c>
+      <c r="FE6" s="2">
+        <v>202.78</v>
+      </c>
+      <c r="FF6" s="2">
+        <v>209.04</v>
+      </c>
+      <c r="FG6" s="2">
+        <v>219.34</v>
+      </c>
+      <c r="FH6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FI6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FJ6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FK6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FL6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FM6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FN6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FO6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FP6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FQ6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FR6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FS6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FT6" s="2">
+        <v>224.72</v>
+      </c>
+      <c r="FU6" s="2">
+        <v>224.72</v>
+      </c>
     </row>
-    <row r="7" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3711,8 +4117,74 @@
       <c r="EY7">
         <v>169.46</v>
       </c>
+      <c r="EZ7" s="2">
+        <v>119.35</v>
+      </c>
+      <c r="FA7" s="2">
+        <v>135.93</v>
+      </c>
+      <c r="FB7" s="2">
+        <v>156.54</v>
+      </c>
+      <c r="FC7" s="2">
+        <v>161.83000000000001</v>
+      </c>
+      <c r="FD7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FE7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FF7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FG7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FH7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FI7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FJ7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FK7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FL7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FM7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FN7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FO7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FP7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FQ7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FR7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FS7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FT7" s="2">
+        <v>165.17</v>
+      </c>
+      <c r="FU7" s="2">
+        <v>165.17</v>
+      </c>
     </row>
-    <row r="8" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4178,8 +4650,74 @@
       <c r="EY8">
         <v>133.72999999999999</v>
       </c>
+      <c r="EZ8" s="2">
+        <v>103.59</v>
+      </c>
+      <c r="FA8" s="2">
+        <v>107.83</v>
+      </c>
+      <c r="FB8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FC8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FD8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FE8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FF8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FG8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FH8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FI8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FJ8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FK8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FL8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FM8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FN8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FO8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FP8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FQ8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FR8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FS8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FT8" s="2">
+        <v>130.34</v>
+      </c>
+      <c r="FU8" s="2">
+        <v>130.34</v>
+      </c>
     </row>
-    <row r="9" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4645,8 +5183,74 @@
       <c r="EY9">
         <v>274.73</v>
       </c>
+      <c r="EZ9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FA9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FB9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FC9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FD9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FE9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FF9" s="2">
+        <v>172.46</v>
+      </c>
+      <c r="FG9" s="2">
+        <v>176.36</v>
+      </c>
+      <c r="FH9" s="2">
+        <v>181.3</v>
+      </c>
+      <c r="FI9" s="2">
+        <v>187.08</v>
+      </c>
+      <c r="FJ9" s="2">
+        <v>192.94</v>
+      </c>
+      <c r="FK9" s="2">
+        <v>202.29</v>
+      </c>
+      <c r="FL9" s="2">
+        <v>210.22</v>
+      </c>
+      <c r="FM9" s="2">
+        <v>218.54</v>
+      </c>
+      <c r="FN9" s="2">
+        <v>231.3</v>
+      </c>
+      <c r="FO9" s="2">
+        <v>231.3</v>
+      </c>
+      <c r="FP9" s="2">
+        <v>242.85</v>
+      </c>
+      <c r="FQ9" s="2">
+        <v>242.85</v>
+      </c>
+      <c r="FR9" s="2">
+        <v>255</v>
+      </c>
+      <c r="FS9" s="2">
+        <v>255</v>
+      </c>
+      <c r="FT9" s="2">
+        <v>267.77</v>
+      </c>
+      <c r="FU9" s="2">
+        <v>267.77</v>
+      </c>
     </row>
-    <row r="10" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5112,8 +5716,74 @@
       <c r="EY10">
         <v>206.59</v>
       </c>
+      <c r="EZ10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FA10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FB10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FC10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FD10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FE10" s="2">
+        <v>141.18</v>
+      </c>
+      <c r="FF10" s="2">
+        <v>147.41999999999999</v>
+      </c>
+      <c r="FG10" s="2">
+        <v>151.29</v>
+      </c>
+      <c r="FH10" s="2">
+        <v>155.91</v>
+      </c>
+      <c r="FI10" s="2">
+        <v>160.94</v>
+      </c>
+      <c r="FJ10" s="2">
+        <v>169.99</v>
+      </c>
+      <c r="FK10" s="2">
+        <v>174.58</v>
+      </c>
+      <c r="FL10" s="2">
+        <v>182.39</v>
+      </c>
+      <c r="FM10" s="2">
+        <v>186.73</v>
+      </c>
+      <c r="FN10" s="2">
+        <v>197.39</v>
+      </c>
+      <c r="FO10" s="2">
+        <v>197.39</v>
+      </c>
+      <c r="FP10" s="2">
+        <v>201.35</v>
+      </c>
+      <c r="FQ10" s="2">
+        <v>201.35</v>
+      </c>
+      <c r="FR10" s="2">
+        <v>201.35</v>
+      </c>
+      <c r="FS10" s="2">
+        <v>201.35</v>
+      </c>
+      <c r="FT10" s="2">
+        <v>201.35</v>
+      </c>
+      <c r="FU10" s="2">
+        <v>201.35</v>
+      </c>
     </row>
-    <row r="11" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5579,8 +6249,74 @@
       <c r="EY11">
         <v>180.97</v>
       </c>
+      <c r="EZ11" s="2">
+        <v>98.14</v>
+      </c>
+      <c r="FA11" s="2">
+        <v>107.11</v>
+      </c>
+      <c r="FB11" s="2">
+        <v>111.22</v>
+      </c>
+      <c r="FC11" s="2">
+        <v>116.64</v>
+      </c>
+      <c r="FD11" s="2">
+        <v>120.89</v>
+      </c>
+      <c r="FE11" s="2">
+        <v>128.16999999999999</v>
+      </c>
+      <c r="FF11" s="2">
+        <v>132.28</v>
+      </c>
+      <c r="FG11" s="2">
+        <v>139.56</v>
+      </c>
+      <c r="FH11" s="2">
+        <v>145.63</v>
+      </c>
+      <c r="FI11" s="2">
+        <v>149.77000000000001</v>
+      </c>
+      <c r="FJ11" s="2">
+        <v>154.16999999999999</v>
+      </c>
+      <c r="FK11" s="2">
+        <v>155.87</v>
+      </c>
+      <c r="FL11" s="2">
+        <v>161.61000000000001</v>
+      </c>
+      <c r="FM11" s="2">
+        <v>164.68</v>
+      </c>
+      <c r="FN11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FO11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FP11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FQ11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FR11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FS11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FT11" s="2">
+        <v>176.38</v>
+      </c>
+      <c r="FU11" s="2">
+        <v>176.38</v>
+      </c>
     </row>
-    <row r="12" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6046,8 +6782,74 @@
       <c r="EY12">
         <v>134.88999999999999</v>
       </c>
+      <c r="EZ12" s="2">
+        <v>84.88</v>
+      </c>
+      <c r="FA12" s="2">
+        <v>93.41</v>
+      </c>
+      <c r="FB12" s="2">
+        <v>97.53</v>
+      </c>
+      <c r="FC12" s="2">
+        <v>101.54</v>
+      </c>
+      <c r="FD12" s="2">
+        <v>105.72</v>
+      </c>
+      <c r="FE12" s="2">
+        <v>115.12</v>
+      </c>
+      <c r="FF12" s="2">
+        <v>118.79</v>
+      </c>
+      <c r="FG12" s="2">
+        <v>125.89</v>
+      </c>
+      <c r="FH12" s="2">
+        <v>128.05000000000001</v>
+      </c>
+      <c r="FI12" s="2">
+        <v>129.63</v>
+      </c>
+      <c r="FJ12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FK12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FL12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FM12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FN12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FO12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FP12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FQ12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FR12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FS12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FT12" s="2">
+        <v>131.47</v>
+      </c>
+      <c r="FU12" s="2">
+        <v>131.47</v>
+      </c>
     </row>
-    <row r="13" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -6513,8 +7315,74 @@
       <c r="EY13">
         <v>113.22</v>
       </c>
+      <c r="EZ13" s="2">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="FA13" s="2">
+        <v>83</v>
+      </c>
+      <c r="FB13" s="2">
+        <v>87.01</v>
+      </c>
+      <c r="FC13" s="2">
+        <v>91.11</v>
+      </c>
+      <c r="FD13" s="2">
+        <v>97.51</v>
+      </c>
+      <c r="FE13" s="2">
+        <v>104.19</v>
+      </c>
+      <c r="FF13" s="2">
+        <v>109.69</v>
+      </c>
+      <c r="FG13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FH13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FI13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FJ13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FK13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FL13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FM13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FN13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FO13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FP13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FQ13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FR13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FS13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FT13" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="FU13" s="2">
+        <v>110.35</v>
+      </c>
     </row>
-    <row r="14" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -6980,8 +7848,74 @@
       <c r="EY14">
         <v>88.8</v>
       </c>
+      <c r="EZ14" s="2">
+        <v>71.3</v>
+      </c>
+      <c r="FA14" s="2">
+        <v>74.95</v>
+      </c>
+      <c r="FB14" s="2">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="FC14" s="2">
+        <v>83.02</v>
+      </c>
+      <c r="FD14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FE14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FF14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FG14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FH14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FI14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FJ14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FK14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FL14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FM14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FN14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FO14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FP14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FQ14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FR14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FS14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FT14" s="2">
+        <v>86.55</v>
+      </c>
+      <c r="FU14" s="2">
+        <v>86.55</v>
+      </c>
     </row>
-    <row r="15" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -7447,8 +8381,74 @@
       <c r="EY15">
         <v>74.45</v>
       </c>
+      <c r="EZ15" s="2">
+        <v>64.37</v>
+      </c>
+      <c r="FA15" s="2">
+        <v>68.41</v>
+      </c>
+      <c r="FB15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FC15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FD15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FE15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FF15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FG15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FH15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FI15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FJ15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FK15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FL15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FM15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FN15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FO15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FP15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FQ15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FR15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FS15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FT15" s="2">
+        <v>72.56</v>
+      </c>
+      <c r="FU15" s="2">
+        <v>72.56</v>
+      </c>
     </row>
-    <row r="16" spans="1:155" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -7914,8 +8914,74 @@
       <c r="EY16">
         <v>62.8</v>
       </c>
+      <c r="EZ16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FA16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FB16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FC16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FD16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FE16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FF16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FG16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FH16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FI16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FJ16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FK16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FL16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FM16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FN16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FO16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FP16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FQ16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FR16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FS16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FT16" s="2">
+        <v>61.21</v>
+      </c>
+      <c r="FU16" s="2">
+        <v>61.21</v>
+      </c>
     </row>
-    <row r="17" spans="1:156" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:177" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -8381,11 +9447,74 @@
       <c r="EY17">
         <v>56.03</v>
       </c>
+      <c r="EZ17">
+        <v>54.61</v>
+      </c>
+      <c r="FA17">
+        <v>54.61</v>
+      </c>
+      <c r="FB17">
+        <v>54.61</v>
+      </c>
+      <c r="FC17">
+        <v>54.61</v>
+      </c>
+      <c r="FD17">
+        <v>54.61</v>
+      </c>
+      <c r="FE17">
+        <v>54.61</v>
+      </c>
+      <c r="FF17">
+        <v>54.61</v>
+      </c>
+      <c r="FG17">
+        <v>54.61</v>
+      </c>
+      <c r="FH17">
+        <v>54.61</v>
+      </c>
+      <c r="FI17">
+        <v>54.61</v>
+      </c>
+      <c r="FJ17">
+        <v>54.61</v>
+      </c>
+      <c r="FK17">
+        <v>54.61</v>
+      </c>
+      <c r="FL17">
+        <v>54.61</v>
+      </c>
+      <c r="FM17">
+        <v>54.61</v>
+      </c>
+      <c r="FN17">
+        <v>54.61</v>
+      </c>
+      <c r="FO17">
+        <v>54.61</v>
+      </c>
+      <c r="FP17">
+        <v>54.61</v>
+      </c>
+      <c r="FQ17">
+        <v>54.61</v>
+      </c>
+      <c r="FR17">
+        <v>54.61</v>
+      </c>
+      <c r="FS17">
+        <v>54.61</v>
+      </c>
+      <c r="FT17">
+        <v>54.61</v>
+      </c>
+      <c r="FU17">
+        <v>54.61</v>
+      </c>
     </row>
-    <row r="22" spans="1:156" x14ac:dyDescent="0.25">
-      <c r="EZ22" s="1"/>
-    </row>
-    <row r="25" spans="1:156" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:177" x14ac:dyDescent="0.25">
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -8409,13 +9538,11 @@
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
     </row>
-    <row r="26" spans="1:156" x14ac:dyDescent="0.25">
-      <c r="EZ26" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="ED28:EY30">
-    <sortCondition descending="1" ref="ED28:ED30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="EO32:FK38">
+    <sortCondition descending="1" ref="EO32:EO38"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
